--- a/demos/sample-data/dimension_wide.xlsx
+++ b/demos/sample-data/dimension_wide.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:KIVI1"/>
+  <dimension ref="A1:XFD1"/>
   <sheetData>
     <row r="1">
       <c r="A1">
